--- a/Daily_Paid_payment_List_Aug_2026.xlsx
+++ b/Daily_Paid_payment_List_Aug_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_Aug_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53735AE-5F13-4E91-A99C-25A341B1528D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FAAB96-CEB2-4554-9FE4-3EA0E5ADD8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" firstSheet="2" activeTab="4" xr2:uid="{E1E8BEB0-7C45-40BF-B119-AC93F03CA3D8}"/>
   </bookViews>
@@ -23,6 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'date_01-08-2026 to 07-08-2026'!$A$3:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'date_08-08-2026 to 14-08-2026'!$A$3:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'date_15-08-2026 to 21-08-2026'!$A$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'date_22-08-2026 to 28-08-2026'!$A$3:$G$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1079,44 +1080,44 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2794,10 +2795,10 @@
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50"/>
       <c r="B10" s="51"/>
-      <c r="C10" s="83" t="s">
+      <c r="C10" s="95" t="s">
         <v>98</v>
       </c>
-      <c r="D10" s="83"/>
+      <c r="D10" s="95"/>
       <c r="E10" s="51">
         <f>SUM(E4:E9)</f>
         <v>1419</v>
@@ -2979,39 +2980,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C1" s="84" t="s">
+      <c r="C1" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="85"/>
-      <c r="E1" s="86"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="91"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="88"/>
-      <c r="E2" s="89"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="94"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3560,6 +3561,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:G3" xr:uid="{3CE48D92-16C9-45EF-8703-7EFFF5AD6FB3}"/>
   <mergeCells count="2">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C2:E2"/>
@@ -3583,18 +3585,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C1" s="84" t="s">
+      <c r="C1" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="85"/>
-      <c r="E1" s="86"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="91"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="88"/>
-      <c r="E2" s="89"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="94"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
@@ -3673,40 +3675,40 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="90">
+      <c r="A7" s="83">
         <v>168</v>
       </c>
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="84" t="s">
         <v>126</v>
       </c>
-      <c r="C7" s="90">
+      <c r="C7" s="83">
         <v>194</v>
       </c>
-      <c r="D7" s="92" t="s">
+      <c r="D7" s="85" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="90">
+      <c r="E7" s="83">
         <v>2340</v>
       </c>
-      <c r="F7" s="90"/>
+      <c r="F7" s="83"/>
       <c r="G7" s="34">
         <f t="shared" si="0"/>
         <v>1740</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="93">
+      <c r="A8" s="86">
         <v>169</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="93"/>
-      <c r="D8" s="95" t="s">
+      <c r="C8" s="86"/>
+      <c r="D8" s="88" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="93"/>
-      <c r="F8" s="93">
+      <c r="E8" s="86"/>
+      <c r="F8" s="86">
         <v>2500</v>
       </c>
       <c r="G8" s="34">
@@ -3718,7 +3720,7 @@
       <c r="A9" s="34">
         <v>170</v>
       </c>
-      <c r="B9" s="91">
+      <c r="B9" s="84">
         <v>46031</v>
       </c>
       <c r="C9" s="34">
@@ -3740,7 +3742,7 @@
       <c r="A10" s="34">
         <v>171</v>
       </c>
-      <c r="B10" s="91">
+      <c r="B10" s="84">
         <v>46031</v>
       </c>
       <c r="C10" s="34">
